--- a/data/content-review-batches/18_rows_171-180.xlsx
+++ b/data/content-review-batches/18_rows_171-180.xlsx
@@ -458,10 +458,8 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>אופן הכנה:
-הכנת הקרם:
-מקציפים במשך 2 דקות את השמנת עם הסוכר ואז מוסיפים את האינסטנט פודינג וחמאת הבוטנים ומקציפים עד לקבלת תערובת יציבה
-בניית הפירמידה:
-בכל פעם מכניסים עוד קצת עם עוגיות היין פנימה על מנת לקבל את מראה הפירמידה
+הכנת הקרם: מקציפים במשך 2 דקות את השמנת עם הסוכר ואז מוסיפים את האינסטנט פודינג וחמאת הבוטנים ומקציפים עד לקבלת תערובת יציבה
+בניית הפירמידה: בכל פעם מכניסים עוד קצת עם עוגיות היין פנימה על מנת לקבל את מראה הפירמידה
 טובלים את עוגיות היין בחלב מסדרים בתבנית ומורחים מעל קרם ממשיכים כך עד שנוצר מראה של פירמידה
 טוחנים 3 עד 4 עוגיות יין למרקם חולי ומדביקים כמו בסרטון על העוגה
 מכניסים למקרר להתייצבות למשך לילה ובתאבון ❤️</t>
@@ -645,14 +643,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-          </t>
+          <t>קל</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-          </t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1145,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-          </t>
+          <t>בינוני</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-          </t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1203,28 +1197,26 @@
 100 גרם סוכר
 50 מ״ל שמנת מתוקה חמה
 25 גרם חמאה
-קורט מלח (לא חובה)</t>
+קורט מלח (לא חובה)
+לקצפת:
+150 מ״ל שמנת מתוקה
+כף אינסטנט פודינג
+כף סוכר
+לקפה:
+קרח
+חלב
+שוט אספרסו
+קרמל (מההכנה)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>אופן הכנת הקרמל:
-בסיר או מחבת שמים את הסוכר ומחממים על אש בינונית עד שהוא נמס והופך לנוזל בצבע ענברי. אין צורך לערבב עם כף – רק לנענע בעדינות את הכלי.
+          <t>אופן הכנת הקרמל: בסיר או מחבת שמים את הסוכר ומחממים על אש בינונית עד שהוא נמס והופך לנוזל בצבע ענברי. אין צורך לערבב עם כף – רק לנענע בעדינות את הכלי.
 כשהסוכר נמס לגמרי, מוסיפים בזהירות את השמנת החמה (מחממים כמה שניות במיקרו) ומערבבים היטב.
 מוסיפים את החמאה וקורט מלח (לא חובה), ומערבבים עד שמתקבל קרמל חלק.
 נותנים לקרמל להתקרר מעט עד שהוא סמיך אך עדיין נוזלי.
 מתקבלת כמות גדולה – ניתן לשמור במקרר או במקפיא לשימוש חוזר.
-לקצפת:
-150 מ״ל שמנת מתוקה
-כף אינסטנט פודינג
-כף סוכר
-מצרכים לקפה:
-קרח
-חלב
-שוט אספרסו
-קרמל (מההכנה)
-הרכבה:
-מקשטים את הכוס בקרמל, מוסיפים קרח, חלב ושוט אספרסו.
+הרכבה: מקשטים את הכוס בקרמל, מוסיפים קרח, חלב ושוט אספרסו.
 מזלפים מעל קצפת, מקשטים בקרמל ונהנים מכל שלוק 🤤🩷⁩</t>
         </is>
       </c>
